--- a/analysis/data/annotation/[Archived] Labeling SDG 1 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 1 - Benchmarking Dataset.xlsx
@@ -6114,7 +6114,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="1.88"/>
+    <col customWidth="1" min="1" max="1" width="30.88"/>
     <col customWidth="1" min="2" max="2" width="91.0"/>
     <col customWidth="1" min="3" max="4" width="19.75"/>
   </cols>
@@ -12017,16 +12017,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="41.25"/>
     <col customWidth="1" min="2" max="2" width="53.13"/>
     <col customWidth="1" min="3" max="3" width="21.75"/>
     <col customWidth="1" min="6" max="6" width="14.38"/>
     <col customWidth="1" min="8" max="8" width="12.75"/>
-    <col customWidth="1" hidden="1" min="10" max="10" width="7.5"/>
-    <col customWidth="1" hidden="1" min="11" max="11" width="7.75"/>
-    <col customWidth="1" hidden="1" min="12" max="12" width="7.25"/>
-    <col customWidth="1" hidden="1" min="13" max="13" width="6.25"/>
-    <col customWidth="1" hidden="1" min="14" max="14" width="8.38"/>
-    <col customWidth="1" hidden="1" min="15" max="15" width="23.88"/>
+    <col customWidth="1" min="10" max="10" width="7.5"/>
+    <col customWidth="1" min="11" max="11" width="7.75"/>
+    <col customWidth="1" min="12" max="12" width="7.25"/>
+    <col customWidth="1" min="13" max="13" width="6.25"/>
+    <col customWidth="1" min="14" max="14" width="8.38"/>
+    <col customWidth="1" min="15" max="15" width="23.88"/>
     <col customWidth="1" min="16" max="16" width="39.75"/>
   </cols>
   <sheetData>
@@ -12130,7 +12131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3">
       <c r="A3" s="36" t="s">
         <v>211</v>
       </c>
@@ -12173,7 +12174,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="4" hidden="1">
+    <row r="4">
       <c r="A4" s="36" t="s">
         <v>158</v>
       </c>
@@ -12421,7 +12422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10">
       <c r="A10" s="36" t="s">
         <v>143</v>
       </c>
@@ -12753,7 +12754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="A18" s="36" t="s">
         <v>257</v>
       </c>
@@ -12794,7 +12795,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="36" t="s">
         <v>71</v>
       </c>
@@ -12962,7 +12963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23">
       <c r="A23" s="36" t="s">
         <v>237</v>
       </c>
@@ -13724,7 +13725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41">
       <c r="A41" s="36" t="s">
         <v>160</v>
       </c>
@@ -13859,7 +13860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" hidden="1">
+    <row r="44">
       <c r="A44" s="36" t="s">
         <v>168</v>
       </c>
@@ -13982,7 +13983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" hidden="1">
+    <row r="47">
       <c r="A47" s="36" t="s">
         <v>115</v>
       </c>
@@ -14195,7 +14196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="A52" s="36" t="s">
         <v>85</v>
       </c>
@@ -14408,7 +14409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" hidden="1">
+    <row r="57">
       <c r="A57" s="36" t="s">
         <v>133</v>
       </c>
@@ -14449,7 +14450,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="58" hidden="1">
+    <row r="58">
       <c r="A58" s="36" t="s">
         <v>99</v>
       </c>
@@ -14619,7 +14620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" hidden="1">
+    <row r="62">
       <c r="A62" s="36" t="s">
         <v>269</v>
       </c>
@@ -15124,7 +15125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74">
       <c r="A74" s="36" t="s">
         <v>118</v>
       </c>
@@ -15169,7 +15170,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75">
       <c r="A75" s="36" t="s">
         <v>273</v>
       </c>
@@ -15212,7 +15213,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" s="36" t="s">
         <v>152</v>
       </c>
@@ -15257,7 +15258,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77">
       <c r="A77" s="36" t="s">
         <v>122</v>
       </c>
@@ -15343,7 +15344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" hidden="1">
+    <row r="79">
       <c r="A79" s="36" t="s">
         <v>106</v>
       </c>
@@ -15766,7 +15767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" s="36" t="s">
         <v>80</v>
       </c>
@@ -15809,7 +15810,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="36" t="s">
         <v>180</v>
       </c>
@@ -16188,7 +16189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" hidden="1">
+    <row r="99">
       <c r="A99" s="36" t="s">
         <v>276</v>
       </c>
@@ -16229,7 +16230,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" s="36" t="s">
         <v>139</v>
       </c>
@@ -16274,7 +16275,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="A101" s="36" t="s">
         <v>182</v>
       </c>
@@ -16318,14 +16319,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$S$101">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="TRUE"/>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$S$101"/>
   <conditionalFormatting sqref="C2:P101">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"TRUE"</formula>
@@ -16388,7 +16382,7 @@
     <row r="2">
       <c r="A2" s="19" t="str">
         <f t="shared" ref="A2:A78" si="1">LEFT(MD5(B2), 7)</f>
-        <v>#NAME?</v>
+        <v>e5a8de3</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>179</v>
@@ -16410,7 +16404,7 @@
     <row r="3">
       <c r="A3" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>b8841e1</v>
       </c>
       <c r="B3" s="50" t="s">
         <v>434</v>
@@ -16435,7 +16429,7 @@
     <row r="4">
       <c r="A4" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>d7796df</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>436</v>
@@ -16460,7 +16454,7 @@
     <row r="5">
       <c r="A5" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>6eb531d</v>
       </c>
       <c r="B5" s="36" t="s">
         <v>70</v>
@@ -16482,7 +16476,7 @@
     <row r="6">
       <c r="A6" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>c66eaf0</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>262</v>
@@ -16504,7 +16498,7 @@
     <row r="7">
       <c r="A7" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>c70d450</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>250</v>
@@ -16526,7 +16520,7 @@
     <row r="8">
       <c r="A8" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>5673db0</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>121</v>
@@ -16548,7 +16542,7 @@
     <row r="9">
       <c r="A9" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>fba9acd</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>266</v>
@@ -16570,7 +16564,7 @@
     <row r="10">
       <c r="A10" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>0c57062</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>437</v>
@@ -16595,7 +16589,7 @@
     <row r="11">
       <c r="A11" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1776f3f</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>260</v>
@@ -16617,7 +16611,7 @@
     <row r="12">
       <c r="A12" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>6569218</v>
       </c>
       <c r="B12" s="36" t="s">
         <v>125</v>
@@ -16639,7 +16633,7 @@
     <row r="13">
       <c r="A13" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>226ce56</v>
       </c>
       <c r="B13" s="36" t="s">
         <v>224</v>
@@ -16661,7 +16655,7 @@
     <row r="14">
       <c r="A14" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>cb7c43e</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>226</v>
@@ -16683,7 +16677,7 @@
     <row r="15">
       <c r="A15" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>5e57da7</v>
       </c>
       <c r="B15" s="36" t="s">
         <v>218</v>
@@ -16705,7 +16699,7 @@
     <row r="16">
       <c r="A16" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>46f112c</v>
       </c>
       <c r="B16" s="36" t="s">
         <v>177</v>
@@ -16727,7 +16721,7 @@
     <row r="17">
       <c r="A17" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>fdff47e</v>
       </c>
       <c r="B17" s="36" t="s">
         <v>202</v>
@@ -16749,7 +16743,7 @@
     <row r="18">
       <c r="A18" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>0f310d4</v>
       </c>
       <c r="B18" s="36" t="s">
         <v>127</v>
@@ -16771,7 +16765,7 @@
     <row r="19">
       <c r="A19" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>adaa428</v>
       </c>
       <c r="B19" s="36" t="s">
         <v>149</v>
@@ -16793,7 +16787,7 @@
     <row r="20">
       <c r="A20" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>9d217d6</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>214</v>
@@ -16815,7 +16809,7 @@
     <row r="21">
       <c r="A21" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>99a1ad8</v>
       </c>
       <c r="B21" s="36" t="s">
         <v>206</v>
@@ -16837,7 +16831,7 @@
     <row r="22">
       <c r="A22" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>9a16ee6</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>438</v>
@@ -16862,7 +16856,7 @@
     <row r="23">
       <c r="A23" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>182044d</v>
       </c>
       <c r="B23" s="36" t="s">
         <v>193</v>
@@ -16887,7 +16881,7 @@
     <row r="24">
       <c r="A24" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>4d3f00a</v>
       </c>
       <c r="B24" s="36" t="s">
         <v>196</v>
@@ -16909,7 +16903,7 @@
     <row r="25">
       <c r="A25" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>2103449</v>
       </c>
       <c r="B25" s="36" t="s">
         <v>138</v>
@@ -16931,7 +16925,7 @@
     <row r="26">
       <c r="A26" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>4548f97</v>
       </c>
       <c r="B26" s="36" t="s">
         <v>268</v>
@@ -16953,7 +16947,7 @@
     <row r="27">
       <c r="A27" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>2af47c6</v>
       </c>
       <c r="B27" s="36" t="s">
         <v>234</v>
@@ -16975,7 +16969,7 @@
     <row r="28">
       <c r="A28" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>16b1c43</v>
       </c>
       <c r="B28" s="36" t="s">
         <v>254</v>
@@ -16997,7 +16991,7 @@
     <row r="29">
       <c r="A29" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1bdad06</v>
       </c>
       <c r="B29" s="36" t="s">
         <v>173</v>
@@ -17019,7 +17013,7 @@
     <row r="30">
       <c r="A30" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>9b64422</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>216</v>
@@ -17041,7 +17035,7 @@
     <row r="31">
       <c r="A31" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>e2b61cb</v>
       </c>
       <c r="B31" s="36" t="s">
         <v>264</v>
@@ -17063,7 +17057,7 @@
     <row r="32">
       <c r="A32" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>421b5ed</v>
       </c>
       <c r="B32" s="36" t="s">
         <v>88</v>
@@ -17085,7 +17079,7 @@
     <row r="33">
       <c r="A33" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>baff0c1</v>
       </c>
       <c r="B33" s="36" t="s">
         <v>147</v>
@@ -17110,7 +17104,7 @@
     <row r="34">
       <c r="A34" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>8e747db</v>
       </c>
       <c r="B34" s="36" t="s">
         <v>200</v>
@@ -17132,7 +17126,7 @@
     <row r="35">
       <c r="A35" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>000a014</v>
       </c>
       <c r="B35" s="36" t="s">
         <v>220</v>
@@ -17154,7 +17148,7 @@
     <row r="36">
       <c r="A36" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>dc07c98</v>
       </c>
       <c r="B36" s="36" t="s">
         <v>109</v>
@@ -17176,7 +17170,7 @@
     <row r="37">
       <c r="A37" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>04da19c</v>
       </c>
       <c r="B37" s="36" t="s">
         <v>90</v>
@@ -17198,7 +17192,7 @@
     <row r="38">
       <c r="A38" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>00a7733</v>
       </c>
       <c r="B38" s="36" t="s">
         <v>185</v>
@@ -17220,7 +17214,7 @@
     <row r="39">
       <c r="A39" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>175bb76</v>
       </c>
       <c r="B39" s="36" t="s">
         <v>230</v>
@@ -17242,7 +17236,7 @@
     <row r="40">
       <c r="A40" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>0288b65</v>
       </c>
       <c r="B40" s="36" t="s">
         <v>236</v>
@@ -17264,7 +17258,7 @@
     <row r="41">
       <c r="A41" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>2e5c49f</v>
       </c>
       <c r="B41" s="36" t="s">
         <v>105</v>
@@ -17286,7 +17280,7 @@
     <row r="42">
       <c r="A42" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>df3840d</v>
       </c>
       <c r="B42" s="36" t="s">
         <v>244</v>
@@ -17308,7 +17302,7 @@
     <row r="43">
       <c r="A43" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>e1368ed</v>
       </c>
       <c r="B43" s="36" t="s">
         <v>228</v>
@@ -17330,7 +17324,7 @@
     <row r="44">
       <c r="A44" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1536114</v>
       </c>
       <c r="B44" s="36" t="s">
         <v>165</v>
@@ -17352,7 +17346,7 @@
     <row r="45">
       <c r="A45" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>9ce6c55</v>
       </c>
       <c r="B45" s="50" t="s">
         <v>439</v>
@@ -17377,7 +17371,7 @@
     <row r="46">
       <c r="A46" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>bcd1591</v>
       </c>
       <c r="B46" s="36" t="s">
         <v>83</v>
@@ -17399,7 +17393,7 @@
     <row r="47">
       <c r="A47" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>173b042</v>
       </c>
       <c r="B47" s="36" t="s">
         <v>256</v>
@@ -17421,7 +17415,7 @@
     <row r="48">
       <c r="A48" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>284e82e</v>
       </c>
       <c r="B48" s="36" t="s">
         <v>208</v>
@@ -17443,7 +17437,7 @@
     <row r="49">
       <c r="A49" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>c1a71dc</v>
       </c>
       <c r="B49" s="36" t="s">
         <v>191</v>
@@ -17465,7 +17459,7 @@
     <row r="50">
       <c r="A50" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>9424dbf</v>
       </c>
       <c r="B50" s="36" t="s">
         <v>240</v>
@@ -17487,7 +17481,7 @@
     <row r="51">
       <c r="A51" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>19953d6</v>
       </c>
       <c r="B51" s="36" t="s">
         <v>167</v>
@@ -17509,7 +17503,7 @@
     <row r="52">
       <c r="A52" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>bf135c7</v>
       </c>
       <c r="B52" s="36" t="s">
         <v>77</v>
@@ -17531,7 +17525,7 @@
     <row r="53">
       <c r="A53" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>35ead2c</v>
       </c>
       <c r="B53" s="36" t="s">
         <v>112</v>
@@ -17553,7 +17547,7 @@
     <row r="54">
       <c r="A54" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>fbbd7df</v>
       </c>
       <c r="B54" s="36" t="s">
         <v>157</v>
@@ -17575,7 +17569,7 @@
     <row r="55">
       <c r="A55" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>8a3fc9c</v>
       </c>
       <c r="B55" s="36" t="s">
         <v>163</v>
@@ -17597,7 +17591,7 @@
     <row r="56">
       <c r="A56" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>08e8c2d</v>
       </c>
       <c r="B56" s="36" t="s">
         <v>131</v>
@@ -17622,7 +17616,7 @@
     <row r="57">
       <c r="A57" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>46f653b</v>
       </c>
       <c r="B57" s="36" t="s">
         <v>189</v>
@@ -17644,7 +17638,7 @@
     <row r="58">
       <c r="A58" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>232849b</v>
       </c>
       <c r="B58" s="36" t="s">
         <v>248</v>
@@ -17666,7 +17660,7 @@
     <row r="59">
       <c r="A59" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>f9ad547</v>
       </c>
       <c r="B59" s="36" t="s">
         <v>102</v>
@@ -17688,7 +17682,7 @@
     <row r="60">
       <c r="A60" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>89efae0</v>
       </c>
       <c r="B60" s="36" t="s">
         <v>79</v>
@@ -17710,7 +17704,7 @@
     <row r="61">
       <c r="A61" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>d7750f4</v>
       </c>
       <c r="B61" s="36" t="s">
         <v>252</v>
@@ -17732,7 +17726,7 @@
     <row r="62">
       <c r="A62" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>68fb390</v>
       </c>
       <c r="B62" s="50" t="s">
         <v>440</v>
@@ -17757,7 +17751,7 @@
     <row r="63">
       <c r="A63" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>8e78df9</v>
       </c>
       <c r="B63" s="36" t="s">
         <v>136</v>
@@ -17779,7 +17773,7 @@
     <row r="64">
       <c r="A64" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>d549972</v>
       </c>
       <c r="B64" s="50" t="s">
         <v>441</v>
@@ -17804,7 +17798,7 @@
     <row r="65">
       <c r="A65" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1242ce8</v>
       </c>
       <c r="B65" s="36" t="s">
         <v>204</v>
@@ -17826,7 +17820,7 @@
     <row r="66">
       <c r="A66" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>abf8c92</v>
       </c>
       <c r="B66" s="36" t="s">
         <v>187</v>
@@ -17848,7 +17842,7 @@
     <row r="67">
       <c r="A67" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1831188</v>
       </c>
       <c r="B67" s="36" t="s">
         <v>210</v>
@@ -17870,7 +17864,7 @@
     <row r="68">
       <c r="A68" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>1db62cd</v>
       </c>
       <c r="B68" s="36" t="s">
         <v>129</v>
@@ -17892,7 +17886,7 @@
     <row r="69">
       <c r="A69" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>984790c</v>
       </c>
       <c r="B69" s="36" t="s">
         <v>142</v>
@@ -17914,7 +17908,7 @@
     <row r="70">
       <c r="A70" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>a173586</v>
       </c>
       <c r="B70" s="36" t="s">
         <v>96</v>
@@ -17936,7 +17930,7 @@
     <row r="71">
       <c r="A71" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>52dd732</v>
       </c>
       <c r="B71" s="36" t="s">
         <v>92</v>
@@ -17958,7 +17952,7 @@
     <row r="72">
       <c r="A72" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>94f2c0b</v>
       </c>
       <c r="B72" s="36" t="s">
         <v>94</v>
@@ -17980,7 +17974,7 @@
     <row r="73">
       <c r="A73" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>57ed03a</v>
       </c>
       <c r="B73" s="36" t="s">
         <v>155</v>
@@ -18002,7 +17996,7 @@
     <row r="74">
       <c r="A74" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>3d656dc</v>
       </c>
       <c r="B74" s="36" t="s">
         <v>198</v>
@@ -18024,7 +18018,7 @@
     <row r="75">
       <c r="A75" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>ac71db1</v>
       </c>
       <c r="B75" s="36" t="s">
         <v>151</v>
@@ -18046,7 +18040,7 @@
     <row r="76">
       <c r="A76" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>fd58c75</v>
       </c>
       <c r="B76" s="36" t="s">
         <v>75</v>
@@ -18068,7 +18062,7 @@
     <row r="77">
       <c r="A77" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>f85780b</v>
       </c>
       <c r="B77" s="36" t="s">
         <v>175</v>
@@ -18090,7 +18084,7 @@
     <row r="78">
       <c r="A78" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>f172dff</v>
       </c>
       <c r="B78" s="36" t="s">
         <v>246</v>
